--- a/S32K1/S32K1xx_Power_Modes _Configuration.xlsx
+++ b/S32K1/S32K1xx_Power_Modes _Configuration.xlsx
@@ -1,15 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" mc:Ignorable="x15">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="6" rupBuild="18431"/>
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="6" rupBuild="28526"/>
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\nxa18217\Desktop\work_projects\S32K1xxDS\rev9\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\nxf88848\Downloads\"/>
     </mc:Choice>
   </mc:AlternateContent>
+  <xr:revisionPtr revIDLastSave="0" documentId="8_{3E5C9FFC-F226-4850-AF37-D719F723848E}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="0" yWindow="0" windowWidth="7608" windowHeight="3792" firstSheet="1" activeTab="1"/>
+    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" firstSheet="1" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Revision" sheetId="6" state="hidden" r:id="rId1"/>
@@ -38,10 +39,21 @@
     <definedName name="slot_size">'[1]Size Data'!$A$2:$A$57</definedName>
     <definedName name="test1">'[5]Size Data'!#REF!</definedName>
   </definedNames>
-  <calcPr calcId="171027"/>
+  <calcPr calcId="191029"/>
   <extLst>
     <ext xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" uri="{140A7094-0E35-4892-8432-C4D2E57EDEB5}">
       <x15:workbookPr chartTrackingRefBase="1"/>
+    </ext>
+    <ext xmlns:xcalcf="http://schemas.microsoft.com/office/spreadsheetml/2018/calcfeatures" uri="{B58B0392-4F1F-4190-BB64-5DF3571DCE5F}">
+      <xcalcf:calcFeatures>
+        <xcalcf:feature name="microsoft.com:RD"/>
+        <xcalcf:feature name="microsoft.com:Single"/>
+        <xcalcf:feature name="microsoft.com:FV"/>
+        <xcalcf:feature name="microsoft.com:CNMTM"/>
+        <xcalcf:feature name="microsoft.com:LET_WF"/>
+        <xcalcf:feature name="microsoft.com:LAMBDA_WF"/>
+        <xcalcf:feature name="microsoft.com:ARRAYTEXT_WF"/>
+      </xcalcf:calcFeatures>
     </ext>
   </extLst>
 </workbook>
@@ -769,7 +781,7 @@
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
-<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" mc:Ignorable="x14ac x16r2">
+<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
   <numFmts count="1">
     <numFmt numFmtId="164" formatCode="[$-409]d\-mmm\-yyyy;@"/>
   </numFmts>
@@ -1044,9 +1056,9 @@
   </cellXfs>
   <cellStyles count="4">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
-    <cellStyle name="Normal 2" xfId="3"/>
-    <cellStyle name="Normal 2 2" xfId="2"/>
-    <cellStyle name="標準 2" xfId="1"/>
+    <cellStyle name="Normal 2" xfId="3" xr:uid="{00000000-0005-0000-0000-000001000000}"/>
+    <cellStyle name="Normal 2 2" xfId="2" xr:uid="{00000000-0005-0000-0000-000002000000}"/>
+    <cellStyle name="標準 2" xfId="1" xr:uid="{00000000-0005-0000-0000-000003000000}"/>
   </cellStyles>
   <dxfs count="0"/>
   <tableStyles count="0" defaultTableStyle="TableStyleMedium2" defaultPivotStyle="PivotStyleLight16"/>
@@ -1062,7 +1074,7 @@
 </file>
 
 <file path=xl/externalLinks/externalLink1.xml><?xml version="1.0" encoding="utf-8"?>
-<externalLink xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" mc:Ignorable="x14">
+<externalLink xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:xxl21="http://schemas.microsoft.com/office/spreadsheetml/2021/extlinks2021" mc:Ignorable="x14 xxl21">
   <externalBook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId1">
     <sheetNames>
       <sheetName val="Title"/>
@@ -1948,7 +1960,7 @@
 </file>
 
 <file path=xl/externalLinks/externalLink2.xml><?xml version="1.0" encoding="utf-8"?>
-<externalLink xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" mc:Ignorable="x14">
+<externalLink xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:xxl21="http://schemas.microsoft.com/office/spreadsheetml/2021/extlinks2021" mc:Ignorable="x14 xxl21">
   <externalBook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId1">
     <sheetNames>
       <sheetName val="Revision History"/>
@@ -2289,7 +2301,7 @@
 </file>
 
 <file path=xl/externalLinks/externalLink3.xml><?xml version="1.0" encoding="utf-8"?>
-<externalLink xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" mc:Ignorable="x14">
+<externalLink xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:xxl21="http://schemas.microsoft.com/office/spreadsheetml/2021/extlinks2021" mc:Ignorable="x14 xxl21">
   <externalBook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId1">
     <sheetNames>
       <sheetName val="Overview Memory Map"/>
@@ -2469,7 +2481,7 @@
 </file>
 
 <file path=xl/externalLinks/externalLink4.xml><?xml version="1.0" encoding="utf-8"?>
-<externalLink xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" mc:Ignorable="x14">
+<externalLink xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:xxl21="http://schemas.microsoft.com/office/spreadsheetml/2021/extlinks2021" mc:Ignorable="x14 xxl21">
   <externalBook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId1">
     <sheetNames>
       <sheetName val="Ownership (non-cust)"/>
@@ -2505,7 +2517,7 @@
 </file>
 
 <file path=xl/externalLinks/externalLink5.xml><?xml version="1.0" encoding="utf-8"?>
-<externalLink xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" mc:Ignorable="x14">
+<externalLink xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:xxl21="http://schemas.microsoft.com/office/spreadsheetml/2021/extlinks2021" mc:Ignorable="x14 xxl21">
   <externalBook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId1">
     <sheetNames>
       <sheetName val="Title"/>
@@ -2853,7 +2865,7 @@
 </file>
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
   <dimension ref="B3:E8"/>
   <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
@@ -2932,7 +2944,7 @@
 </file>
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0100-000000000000}">
   <dimension ref="A1:A4"/>
   <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
@@ -2963,7 +2975,7 @@
 </file>
 
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0200-000000000000}">
   <dimension ref="A1:C8"/>
   <sheetFormatPr defaultColWidth="9.109375" defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
@@ -3053,7 +3065,7 @@
 </file>
 
 <file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0300-000000000000}">
   <dimension ref="A1:P50"/>
   <sheetFormatPr defaultColWidth="15.6640625" defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
@@ -5321,7 +5333,7 @@
 </file>
 
 <file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0400-000000000000}">
   <dimension ref="A1:K46"/>
   <sheetFormatPr defaultColWidth="15.6640625" defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
@@ -6667,6 +6679,23 @@
 </file>
 
 <file path=customXml/item1.xml><?xml version="1.0" encoding="utf-8"?>
+<?mso-contentType ?>
+<FormTemplates xmlns="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms">
+  <Display>DocumentLibraryForm</Display>
+  <Edit>DocumentLibraryForm</Edit>
+  <New>DocumentLibraryForm</New>
+</FormTemplates>
+</file>
+
+<file path=customXml/item2.xml><?xml version="1.0" encoding="utf-8"?>
+<p:properties xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:xsi="http://www.w3.org/2001/XMLSchema-instance" xmlns:pc="http://schemas.microsoft.com/office/infopath/2007/PartnerControls">
+  <documentManagement>
+    <IconOverlay xmlns="http://schemas.microsoft.com/sharepoint/v4" xsi:nil="true"/>
+  </documentManagement>
+</p:properties>
+</file>
+
+<file path=customXml/item3.xml><?xml version="1.0" encoding="utf-8"?>
 <ct:contentTypeSchema xmlns:ct="http://schemas.microsoft.com/office/2006/metadata/contentType" xmlns:ma="http://schemas.microsoft.com/office/2006/metadata/properties/metaAttributes" ct:_="" ma:_="" ma:contentTypeName="Document" ma:contentTypeID="0x01010062FD28AF48F86F4199F875DC48D7571E" ma:contentTypeVersion="11" ma:contentTypeDescription="Create a new document." ma:contentTypeScope="" ma:versionID="9f42406e585640ec5f24368115178850">
   <xsd:schema xmlns:xsd="http://www.w3.org/2001/XMLSchema" xmlns:xs="http://www.w3.org/2001/XMLSchema" xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:ns2="6dd24d01-1828-4579-8bd7-ef8e5a7c81f8" xmlns:ns3="http://schemas.microsoft.com/sharepoint/v4" xmlns:ns4="f39b4ec7-cd2a-4b1f-9221-6df9735d305b" targetNamespace="http://schemas.microsoft.com/office/2006/metadata/properties" ma:root="true" ma:fieldsID="222f0c8a663df0aa884c7c7380d699e2" ns2:_="" ns3:_="" ns4:_="">
     <xsd:import namespace="6dd24d01-1828-4579-8bd7-ef8e5a7c81f8"/>
@@ -6882,39 +6911,10 @@
 </ct:contentTypeSchema>
 </file>
 
-<file path=customXml/item2.xml><?xml version="1.0" encoding="utf-8"?>
-<p:properties xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:xsi="http://www.w3.org/2001/XMLSchema-instance" xmlns:pc="http://schemas.microsoft.com/office/infopath/2007/PartnerControls">
-  <documentManagement>
-    <IconOverlay xmlns="http://schemas.microsoft.com/sharepoint/v4" xsi:nil="true"/>
-  </documentManagement>
-</p:properties>
-</file>
-
-<file path=customXml/item3.xml><?xml version="1.0" encoding="utf-8"?>
-<?mso-contentType ?>
-<FormTemplates xmlns="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms">
-  <Display>DocumentLibraryForm</Display>
-  <Edit>DocumentLibraryForm</Edit>
-  <New>DocumentLibraryForm</New>
-</FormTemplates>
-</file>
-
 <file path=customXml/itemProps1.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{67545D62-1594-498E-B926-5D672AAF26BA}">
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{68D695D2-4B97-48C6-81A0-BF3D449F42BC}">
   <ds:schemaRefs>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/metadata/contentType"/>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/metadata/properties/metaAttributes"/>
-    <ds:schemaRef ds:uri="http://www.w3.org/2001/XMLSchema"/>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/metadata/properties"/>
-    <ds:schemaRef ds:uri="6dd24d01-1828-4579-8bd7-ef8e5a7c81f8"/>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/sharepoint/v4"/>
-    <ds:schemaRef ds:uri="f39b4ec7-cd2a-4b1f-9221-6df9735d305b"/>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/documentManagement/types"/>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
-    <ds:schemaRef ds:uri="http://schemas.openxmlformats.org/package/2006/metadata/core-properties"/>
-    <ds:schemaRef ds:uri="http://purl.org/dc/elements/1.1/"/>
-    <ds:schemaRef ds:uri="http://purl.org/dc/terms/"/>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/internal/obd"/>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms"/>
   </ds:schemaRefs>
 </ds:datastoreItem>
 </file>
@@ -6938,9 +6938,21 @@
 </file>
 
 <file path=customXml/itemProps3.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{68D695D2-4B97-48C6-81A0-BF3D449F42BC}">
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{67545D62-1594-498E-B926-5D672AAF26BA}">
   <ds:schemaRefs>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms"/>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/metadata/contentType"/>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/metadata/properties/metaAttributes"/>
+    <ds:schemaRef ds:uri="http://www.w3.org/2001/XMLSchema"/>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/metadata/properties"/>
+    <ds:schemaRef ds:uri="6dd24d01-1828-4579-8bd7-ef8e5a7c81f8"/>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/sharepoint/v4"/>
+    <ds:schemaRef ds:uri="f39b4ec7-cd2a-4b1f-9221-6df9735d305b"/>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/documentManagement/types"/>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
+    <ds:schemaRef ds:uri="http://schemas.openxmlformats.org/package/2006/metadata/core-properties"/>
+    <ds:schemaRef ds:uri="http://purl.org/dc/elements/1.1/"/>
+    <ds:schemaRef ds:uri="http://purl.org/dc/terms/"/>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/internal/obd"/>
   </ds:schemaRefs>
 </ds:datastoreItem>
 </file>